--- a/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_18h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -497,8 +497,8 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
-        <v>4</v>
+      <c r="D8">
+        <v>23.4</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -525,8 +525,8 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
-        <v>4</v>
+      <c r="D10">
+        <v>21.6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -553,8 +553,8 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" t="s">
-        <v>4</v>
+      <c r="D12">
+        <v>24.4</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -567,8 +567,8 @@
       <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13" t="s">
-        <v>4</v>
+      <c r="D13">
+        <v>22.9</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -581,8 +581,8 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14" t="s">
-        <v>4</v>
+      <c r="D14">
+        <v>23.8</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -595,8 +595,8 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" t="s">
-        <v>4</v>
+      <c r="D15">
+        <v>24.6</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -609,8 +609,8 @@
       <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16" t="s">
-        <v>4</v>
+      <c r="D16">
+        <v>24.6</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -624,7 +624,7 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>22.8</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -638,7 +638,7 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -693,8 +693,8 @@
       <c r="C22">
         <v>21</v>
       </c>
-      <c r="D22" t="s">
-        <v>4</v>
+      <c r="D22">
+        <v>23.8</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -707,8 +707,8 @@
       <c r="C23">
         <v>22</v>
       </c>
-      <c r="D23" t="s">
-        <v>4</v>
+      <c r="D23">
+        <v>23.8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -721,8 +721,8 @@
       <c r="C24">
         <v>23</v>
       </c>
-      <c r="D24" t="s">
-        <v>4</v>
+      <c r="D24">
+        <v>24.8</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -735,8 +735,8 @@
       <c r="C25">
         <v>24</v>
       </c>
-      <c r="D25" t="s">
-        <v>4</v>
+      <c r="D25">
+        <v>23.5</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -749,8 +749,8 @@
       <c r="C26">
         <v>25</v>
       </c>
-      <c r="D26" t="s">
-        <v>4</v>
+      <c r="D26">
+        <v>24.6</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -778,7 +778,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>23.8</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -806,7 +806,7 @@
         <v>29</v>
       </c>
       <c r="D30">
-        <v>22.5</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -820,7 +820,7 @@
         <v>30</v>
       </c>
       <c r="D31">
-        <v>23.6</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -848,7 +848,7 @@
         <v>1</v>
       </c>
       <c r="D33">
-        <v>24.9</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -862,7 +862,7 @@
         <v>2</v>
       </c>
       <c r="D34">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -876,7 +876,7 @@
         <v>3</v>
       </c>
       <c r="D35">
-        <v>24.8</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -904,7 +904,7 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -918,7 +918,7 @@
         <v>6</v>
       </c>
       <c r="D38">
-        <v>25.1</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -931,8 +931,8 @@
       <c r="C39">
         <v>7</v>
       </c>
-      <c r="D39">
-        <v>25.6</v>
+      <c r="D39" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -945,8 +945,8 @@
       <c r="C40">
         <v>8</v>
       </c>
-      <c r="D40">
-        <v>22.8</v>
+      <c r="D40" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -959,8 +959,8 @@
       <c r="C41">
         <v>9</v>
       </c>
-      <c r="D41">
-        <v>24</v>
+      <c r="D41" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -988,7 +988,7 @@
         <v>11</v>
       </c>
       <c r="D43">
-        <v>24</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1030,7 +1030,7 @@
         <v>14</v>
       </c>
       <c r="D46">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1044,7 +1044,7 @@
         <v>15</v>
       </c>
       <c r="D47">
-        <v>22</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1057,8 +1057,8 @@
       <c r="C48">
         <v>16</v>
       </c>
-      <c r="D48" t="s">
-        <v>4</v>
+      <c r="D48">
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1085,8 +1085,8 @@
       <c r="C50">
         <v>18</v>
       </c>
-      <c r="D50" t="s">
-        <v>4</v>
+      <c r="D50">
+        <v>25.5</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1099,8 +1099,8 @@
       <c r="C51">
         <v>19</v>
       </c>
-      <c r="D51" t="s">
-        <v>4</v>
+      <c r="D51">
+        <v>22.6</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1114,7 +1114,7 @@
         <v>20</v>
       </c>
       <c r="D52">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1128,7 +1128,7 @@
         <v>21</v>
       </c>
       <c r="D53">
-        <v>23.6</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1142,7 +1142,7 @@
         <v>22</v>
       </c>
       <c r="D54">
-        <v>21.6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1169,8 +1169,8 @@
       <c r="C56">
         <v>24</v>
       </c>
-      <c r="D56" t="s">
-        <v>4</v>
+      <c r="D56">
+        <v>24.4</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1183,8 +1183,8 @@
       <c r="C57">
         <v>25</v>
       </c>
-      <c r="D57" t="s">
-        <v>4</v>
+      <c r="D57">
+        <v>20.8</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1198,7 +1198,7 @@
         <v>26</v>
       </c>
       <c r="D58">
-        <v>22.5</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="59" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_18h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Wet_bulb_temp_18h00</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -483,8 +480,8 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>4</v>
+      <c r="D7">
+        <v>24.1</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -511,8 +508,8 @@
       <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9" t="s">
-        <v>4</v>
+      <c r="D9">
+        <v>23.7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -554,7 +551,7 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>24.4</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -568,7 +565,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -582,7 +579,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>23.8</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -596,7 +593,7 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>24.6</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -610,7 +607,7 @@
         <v>15</v>
       </c>
       <c r="D16">
-        <v>24.6</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -638,7 +635,7 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>22.8</v>
+        <v>22.4</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -652,7 +649,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>24.4</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -694,7 +691,7 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>23.8</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -722,7 +719,7 @@
         <v>23</v>
       </c>
       <c r="D24">
-        <v>24.8</v>
+        <v>23.9</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -736,7 +733,7 @@
         <v>24</v>
       </c>
       <c r="D25">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -750,7 +747,7 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>24.6</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -792,7 +789,7 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>23.4</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -834,7 +831,7 @@
         <v>31</v>
       </c>
       <c r="D32">
-        <v>26.3</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -904,7 +901,7 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>24.4</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -931,8 +928,8 @@
       <c r="C39">
         <v>7</v>
       </c>
-      <c r="D39" t="s">
-        <v>4</v>
+      <c r="D39">
+        <v>24.3</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -945,8 +942,8 @@
       <c r="C40">
         <v>8</v>
       </c>
-      <c r="D40" t="s">
-        <v>4</v>
+      <c r="D40">
+        <v>22.8</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -959,8 +956,8 @@
       <c r="C41">
         <v>9</v>
       </c>
-      <c r="D41" t="s">
-        <v>4</v>
+      <c r="D41">
+        <v>23.3</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -988,7 +985,7 @@
         <v>11</v>
       </c>
       <c r="D43">
-        <v>25.1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1030,7 +1027,7 @@
         <v>14</v>
       </c>
       <c r="D46">
-        <v>24.2</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1044,7 +1041,7 @@
         <v>15</v>
       </c>
       <c r="D47">
-        <v>22.6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1086,7 +1083,7 @@
         <v>18</v>
       </c>
       <c r="D50">
-        <v>25.5</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1100,7 +1097,7 @@
         <v>19</v>
       </c>
       <c r="D51">
-        <v>22.6</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1114,7 +1111,7 @@
         <v>20</v>
       </c>
       <c r="D52">
-        <v>22.6</v>
+        <v>21.7</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1128,7 +1125,7 @@
         <v>21</v>
       </c>
       <c r="D53">
-        <v>24.9</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1170,7 +1167,7 @@
         <v>24</v>
       </c>
       <c r="D56">
-        <v>24.4</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1184,7 +1181,7 @@
         <v>25</v>
       </c>
       <c r="D57">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1226,7 +1223,7 @@
         <v>28</v>
       </c>
       <c r="D60">
-        <v>24.5</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1240,7 +1237,7 @@
         <v>29</v>
       </c>
       <c r="D61">
-        <v>24.6</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="62" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_18h00_timeseries.xlsx
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>23.8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -733,7 +733,7 @@
         <v>24</v>
       </c>
       <c r="D25">
-        <v>24.6</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="26" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_18h00_timeseries.xlsx
@@ -705,7 +705,7 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>23</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -775,7 +775,7 @@
         <v>27</v>
       </c>
       <c r="D28">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1181,7 +1181,7 @@
         <v>25</v>
       </c>
       <c r="D57">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="58" spans="1:4">

--- a/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_18h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Wet_bulb_temp_18h00_timeseries.xlsx
@@ -411,7 +411,7 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>21.9</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -439,7 +439,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>21.8</v>
+        <v>23.7</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -481,7 +481,7 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>24.1</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -495,7 +495,7 @@
         <v>7</v>
       </c>
       <c r="D8">
-        <v>23.4</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -509,7 +509,7 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>23.7</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -537,7 +537,7 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>23.4</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -551,7 +551,7 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>22.9</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -565,7 +565,7 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -579,7 +579,7 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>22.5</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -593,7 +593,7 @@
         <v>14</v>
       </c>
       <c r="D15">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -607,7 +607,7 @@
         <v>15</v>
       </c>
       <c r="D16">
-        <v>23.9</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -621,7 +621,7 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>22.2</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -635,7 +635,7 @@
         <v>17</v>
       </c>
       <c r="D18">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -649,7 +649,7 @@
         <v>18</v>
       </c>
       <c r="D19">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -663,7 +663,7 @@
         <v>19</v>
       </c>
       <c r="D20">
-        <v>23.2</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -691,7 +691,7 @@
         <v>21</v>
       </c>
       <c r="D22">
-        <v>22.5</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -719,7 +719,7 @@
         <v>23</v>
       </c>
       <c r="D24">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -733,7 +733,7 @@
         <v>24</v>
       </c>
       <c r="D25">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -747,7 +747,7 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>23.1</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -789,7 +789,7 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>22.9</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -831,7 +831,7 @@
         <v>31</v>
       </c>
       <c r="D32">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -845,7 +845,7 @@
         <v>1</v>
       </c>
       <c r="D33">
-        <v>23.6</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -873,7 +873,7 @@
         <v>3</v>
       </c>
       <c r="D35">
-        <v>23.5</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -887,7 +887,7 @@
         <v>4</v>
       </c>
       <c r="D36">
-        <v>23.4</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -901,7 +901,7 @@
         <v>5</v>
       </c>
       <c r="D37">
-        <v>23.1</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -915,7 +915,7 @@
         <v>6</v>
       </c>
       <c r="D38">
-        <v>23.5</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -929,7 +929,7 @@
         <v>7</v>
       </c>
       <c r="D39">
-        <v>24.3</v>
+        <v>25.6</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -943,7 +943,7 @@
         <v>8</v>
       </c>
       <c r="D40">
-        <v>22.8</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -957,7 +957,7 @@
         <v>9</v>
       </c>
       <c r="D41">
-        <v>23.3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -971,7 +971,7 @@
         <v>10</v>
       </c>
       <c r="D42">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -985,7 +985,7 @@
         <v>11</v>
       </c>
       <c r="D43">
-        <v>24</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -999,7 +999,7 @@
         <v>12</v>
       </c>
       <c r="D44">
-        <v>23.6</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1013,7 +1013,7 @@
         <v>13</v>
       </c>
       <c r="D45">
-        <v>21.9</v>
+        <v>22.8</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1027,7 +1027,7 @@
         <v>14</v>
       </c>
       <c r="D46">
-        <v>23.4</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1041,7 +1041,7 @@
         <v>15</v>
       </c>
       <c r="D47">
-        <v>22</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1069,7 +1069,7 @@
         <v>17</v>
       </c>
       <c r="D49">
-        <v>22.2</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1083,7 +1083,7 @@
         <v>18</v>
       </c>
       <c r="D50">
-        <v>24.2</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1097,7 +1097,7 @@
         <v>19</v>
       </c>
       <c r="D51">
-        <v>21.9</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1111,7 +1111,7 @@
         <v>20</v>
       </c>
       <c r="D52">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1125,7 +1125,7 @@
         <v>21</v>
       </c>
       <c r="D53">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1153,7 +1153,7 @@
         <v>23</v>
       </c>
       <c r="D55">
-        <v>18.6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1167,7 +1167,7 @@
         <v>24</v>
       </c>
       <c r="D56">
-        <v>23.7</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1223,7 +1223,7 @@
         <v>28</v>
       </c>
       <c r="D60">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1237,7 +1237,7 @@
         <v>29</v>
       </c>
       <c r="D61">
-        <v>23.7</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="62" spans="1:4">
